--- a/docs/06-execution/regression-results.xlsx
+++ b/docs/06-execution/regression-results.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>evidence/smoke/TC-AUTH-007-after-logout.png (flow re-verified this build, lands login — batch log)</t>
+          <t>evidence/smoke/TC-AUTH-007-after-logout.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Phase 10 batch log</t>
+          <t>evidence/smoke/TC-PIM-001-created-E2091.png</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -780,6 +780,11 @@
           <t>No pending request exists (blocked submit upstream); nothing to cancel</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>evidence/smoke/TC-LEAVE-002-ess-apply-form.png; evidence/regression/REG-008-leave-list.png</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>2026-10-03</t>
@@ -814,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>evidence/regression/REG-010-punched-in/out + my-records.png</t>
+          <t>evidence/regression/REG-010-punched-in.png; evidence/regression/REG-010-punched-out.png; evidence/regression/REG-010-my-records.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
